--- a/artfynd/A 28785-2026 artfynd.xlsx
+++ b/artfynd/A 28785-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136373213</v>
       </c>
       <c r="B4" t="n">
-        <v>92902</v>
+        <v>92905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136373236</v>
       </c>
       <c r="B5" t="n">
-        <v>92902</v>
+        <v>92905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136373238</v>
       </c>
       <c r="B10" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136373245</v>
       </c>
       <c r="B11" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>136373237</v>
       </c>
       <c r="B14" t="n">
-        <v>96645</v>
+        <v>96648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>136373204</v>
       </c>
       <c r="B16" t="n">
-        <v>92663</v>
+        <v>92666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>136373239</v>
       </c>
       <c r="B20" t="n">
-        <v>92086</v>
+        <v>92089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136373241</v>
       </c>
       <c r="B21" t="n">
-        <v>90081</v>
+        <v>90083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136373246</v>
       </c>
       <c r="B26" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136373200</v>
       </c>
       <c r="B29" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136373207</v>
       </c>
       <c r="B30" t="n">
-        <v>98198</v>
+        <v>98201</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136373201</v>
       </c>
       <c r="B33" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136373218</v>
       </c>
       <c r="B34" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>136373222</v>
       </c>
       <c r="B35" t="n">
-        <v>103637</v>
+        <v>103640</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 28785-2026 artfynd.xlsx
+++ b/artfynd/A 28785-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136373213</v>
       </c>
       <c r="B4" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136373236</v>
       </c>
       <c r="B5" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136373238</v>
       </c>
       <c r="B10" t="n">
-        <v>96659</v>
+        <v>96660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136373245</v>
       </c>
       <c r="B11" t="n">
-        <v>96659</v>
+        <v>96660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>136373237</v>
       </c>
       <c r="B14" t="n">
-        <v>96648</v>
+        <v>96649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>136373204</v>
       </c>
       <c r="B16" t="n">
-        <v>92666</v>
+        <v>92667</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>136373239</v>
       </c>
       <c r="B20" t="n">
-        <v>92089</v>
+        <v>92090</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136373246</v>
       </c>
       <c r="B26" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136373200</v>
       </c>
       <c r="B29" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136373207</v>
       </c>
       <c r="B30" t="n">
-        <v>98201</v>
+        <v>98202</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136373201</v>
       </c>
       <c r="B33" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136373218</v>
       </c>
       <c r="B34" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>136373222</v>
       </c>
       <c r="B35" t="n">
-        <v>103640</v>
+        <v>103641</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 28785-2026 artfynd.xlsx
+++ b/artfynd/A 28785-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136373213</v>
       </c>
       <c r="B4" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136373236</v>
       </c>
       <c r="B5" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136373238</v>
       </c>
       <c r="B10" t="n">
-        <v>96660</v>
+        <v>96665</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136373245</v>
       </c>
       <c r="B11" t="n">
-        <v>96660</v>
+        <v>96665</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>136373237</v>
       </c>
       <c r="B14" t="n">
-        <v>96649</v>
+        <v>96654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>136373204</v>
       </c>
       <c r="B16" t="n">
-        <v>92667</v>
+        <v>92672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>136373239</v>
       </c>
       <c r="B20" t="n">
-        <v>92090</v>
+        <v>92095</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136373241</v>
       </c>
       <c r="B21" t="n">
-        <v>90083</v>
+        <v>90085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>136373228</v>
       </c>
       <c r="B25" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136373246</v>
       </c>
       <c r="B26" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136373200</v>
       </c>
       <c r="B29" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136373207</v>
       </c>
       <c r="B30" t="n">
-        <v>98202</v>
+        <v>98207</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136373201</v>
       </c>
       <c r="B33" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136373218</v>
       </c>
       <c r="B34" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>136373222</v>
       </c>
       <c r="B35" t="n">
-        <v>103641</v>
+        <v>103646</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 28785-2026 artfynd.xlsx
+++ b/artfynd/A 28785-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136373213</v>
       </c>
       <c r="B4" t="n">
-        <v>92911</v>
+        <v>92913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136373236</v>
       </c>
       <c r="B5" t="n">
-        <v>92911</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136373238</v>
       </c>
       <c r="B10" t="n">
-        <v>96665</v>
+        <v>96667</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136373245</v>
       </c>
       <c r="B11" t="n">
-        <v>96665</v>
+        <v>96667</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>136373237</v>
       </c>
       <c r="B14" t="n">
-        <v>96654</v>
+        <v>96656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>136373204</v>
       </c>
       <c r="B16" t="n">
-        <v>92672</v>
+        <v>92674</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>136373239</v>
       </c>
       <c r="B20" t="n">
-        <v>92095</v>
+        <v>92097</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136373241</v>
       </c>
       <c r="B21" t="n">
-        <v>90085</v>
+        <v>90087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136373246</v>
       </c>
       <c r="B26" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136373200</v>
       </c>
       <c r="B29" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136373207</v>
       </c>
       <c r="B30" t="n">
-        <v>98207</v>
+        <v>98209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136373201</v>
       </c>
       <c r="B33" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136373218</v>
       </c>
       <c r="B34" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>136373222</v>
       </c>
       <c r="B35" t="n">
-        <v>103646</v>
+        <v>103648</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 28785-2026 artfynd.xlsx
+++ b/artfynd/A 28785-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136373213</v>
       </c>
       <c r="B4" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136373236</v>
       </c>
       <c r="B5" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136373238</v>
       </c>
       <c r="B10" t="n">
-        <v>96667</v>
+        <v>96673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136373245</v>
       </c>
       <c r="B11" t="n">
-        <v>96667</v>
+        <v>96673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>136373237</v>
       </c>
       <c r="B14" t="n">
-        <v>96656</v>
+        <v>96662</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>136373204</v>
       </c>
       <c r="B16" t="n">
-        <v>92674</v>
+        <v>92676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>136373239</v>
       </c>
       <c r="B20" t="n">
-        <v>92097</v>
+        <v>92099</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136373241</v>
       </c>
       <c r="B21" t="n">
-        <v>90087</v>
+        <v>90089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136373246</v>
       </c>
       <c r="B26" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136373200</v>
       </c>
       <c r="B29" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136373207</v>
       </c>
       <c r="B30" t="n">
-        <v>98209</v>
+        <v>98215</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136373201</v>
       </c>
       <c r="B33" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136373218</v>
       </c>
       <c r="B34" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>136373222</v>
       </c>
       <c r="B35" t="n">
-        <v>103648</v>
+        <v>103654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 28785-2026 artfynd.xlsx
+++ b/artfynd/A 28785-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136373213</v>
       </c>
       <c r="B4" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136373236</v>
       </c>
       <c r="B5" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>136373238</v>
       </c>
       <c r="B10" t="n">
-        <v>96673</v>
+        <v>96675</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136373245</v>
       </c>
       <c r="B11" t="n">
-        <v>96673</v>
+        <v>96675</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>136373237</v>
       </c>
       <c r="B14" t="n">
-        <v>96662</v>
+        <v>96664</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>136373204</v>
       </c>
       <c r="B16" t="n">
-        <v>92676</v>
+        <v>92678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>136373239</v>
       </c>
       <c r="B20" t="n">
-        <v>92099</v>
+        <v>92101</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136373241</v>
       </c>
       <c r="B21" t="n">
-        <v>90089</v>
+        <v>90091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136373246</v>
       </c>
       <c r="B26" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>136373200</v>
       </c>
       <c r="B29" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136373207</v>
       </c>
       <c r="B30" t="n">
-        <v>98215</v>
+        <v>98217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136373201</v>
       </c>
       <c r="B33" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>136373218</v>
       </c>
       <c r="B34" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>136373222</v>
       </c>
       <c r="B35" t="n">
-        <v>103654</v>
+        <v>103656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
